--- a/modification-resultats-mapping/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/modification-resultats-mapping/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:11:05+00:00</t>
+    <t>2026-07-10T12:16:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
